--- a/DEV/org.openl.rules/test/rules/binding/VarArgsMethodBindingTest.xlsx
+++ b/DEV/org.openl.rules/test/rules/binding/VarArgsMethodBindingTest.xlsx
@@ -33,8 +33,8 @@
   </si>
   <si>
     <t>int sum = 0;
-for (int j=0;j&lt;values.length; j++) {
-for (int i=0; i&lt; values[j].length; i++) {
+for (int j=0;j&lt;values.length; j += 1) {
+for (int i=0; i&lt; values[j].length; i += 1) {
 sum+=values[j][i];
 }}
 return sum;</t>
